--- a/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
@@ -539,10 +539,10 @@
         <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="n">
-        <v>46.2</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>0.18</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H13" t="n">
-        <v>20.7</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="14">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>133.1</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="17">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>192.9</v>
+        <v>173.78</v>
       </c>
       <c r="H26" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="27">
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>194.83</v>
+        <v>175.52</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
@@ -643,10 +643,10 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>37.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="15">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>113.98</v>
+        <v>95.98</v>
       </c>
     </row>
     <row r="17">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>173.78</v>
+        <v>155.78</v>
       </c>
       <c r="H26" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="27">
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>175.52</v>
+        <v>157.34</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-14-04-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 14 Instalaciones mecánicas y especiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Sistemas de respaldo eléctrico</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
